--- a/jira_export_2026-07-10.xlsx
+++ b/jira_export_2026-07-10.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>12,225 €</t>
+          <t>19,663 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,14 +769,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>3,139 €</t>
+          <t>3,800 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>9,086 €</t>
+          <t>15,863 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -1974,10 +1974,10 @@
         <v>3207.7</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>3207.7</v>
+        <v>4170.01</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>1069.23</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="18">
@@ -2262,10 +2262,10 @@
         <v>280</v>
       </c>
       <c r="O21" s="17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22">
@@ -2478,10 +2478,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>248.58</v>
+        <v>497.16</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>58.49</v>
+        <v>116.98</v>
       </c>
     </row>
     <row r="25">
@@ -2622,10 +2622,10 @@
         <v>2100</v>
       </c>
       <c r="O26" s="17" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0</v>
+        <v>509.09</v>
       </c>
     </row>
     <row r="27">
@@ -4557,11 +4557,11 @@
       <c r="N53" s="13" t="n">
         <v>3621</v>
       </c>
-      <c r="O53" s="17" t="n">
-        <v>0</v>
+      <c r="O53" s="13" t="n">
+        <v>4224.5</v>
       </c>
       <c r="P53" s="13" t="n">
-        <v>0</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="54">
@@ -5854,10 +5854,10 @@
         <v>1046.5</v>
       </c>
       <c r="O71" s="17" t="n">
-        <v>455</v>
+        <v>637</v>
       </c>
       <c r="P71" s="13" t="n">
-        <v>53.53</v>
+        <v>74.94</v>
       </c>
     </row>
     <row r="72">
@@ -5998,10 +5998,10 @@
         <v>0</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>0</v>
+        <v>133.33</v>
       </c>
     </row>
     <row r="74">
@@ -9132,10 +9132,10 @@
         <v>0</v>
       </c>
       <c r="O117" s="13" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="P117" s="13" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="118">
@@ -12302,10 +12302,10 @@
         <v>70028.95999999999</v>
       </c>
       <c r="O165" s="19" t="n">
-        <v>12225.38</v>
+        <v>19662.77</v>
       </c>
       <c r="P165" s="19" t="n">
-        <v>72.89</v>
+        <v>117.24</v>
       </c>
     </row>
   </sheetData>
@@ -13191,16 +13191,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>410108</v>
+        <v>402670</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>210303</v>
+        <v>207320</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>199805</v>
+        <v>195350</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>160398</v>
+        <v>155944</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>24017</v>
@@ -13216,16 +13216,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>189271</v>
+        <v>188611</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>82119</v>
+        <v>81688</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>107152</v>
+        <v>106922</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>92854</v>
+        <v>92624</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>10060</v>
@@ -13241,16 +13241,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>220836</v>
+        <v>214060</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>128184</v>
+        <v>125632</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>92652</v>
+        <v>88428</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>67544</v>
+        <v>63320</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>13957</v>

--- a/jira_export_2026-07-10.xlsx
+++ b/jira_export_2026-07-10.xlsx
@@ -736,14 +736,14 @@
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>132,000 €</t>
+          <t>95,000 €</t>
         </is>
       </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -783,7 +783,7 @@
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>74,500 / 57,500 €</t>
+          <t>38,000 / 57,000 €</t>
         </is>
       </c>
       <c r="H11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>271 h</t>
+          <t>273 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>4170.01</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>1390</v>
+        <v>926.67</v>
       </c>
     </row>
     <row r="18">
@@ -9188,7 +9188,7 @@
         <v>8</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>19662.77</v>
       </c>
       <c r="P165" s="19" t="n">
-        <v>117.24</v>
+        <v>115.85</v>
       </c>
     </row>
   </sheetData>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>97</v>
+        <v>97.5</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>27</v>
@@ -13054,7 +13054,7 @@
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>124.75</v>
+        <v>125.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>28</v>
@@ -13064,7 +13064,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.8%</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>4.75</v>
@@ -13084,7 +13084,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>41.25</v>
+        <v>42.75</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>11</v>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-07-10.xlsx
+++ b/jira_export_2026-07-10.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>289 h</t>
+          <t>296 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1810,7 +1810,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>720</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>99.31</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -11198,7 +11198,7 @@
         <v>19</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="L147" s="12" t="inlineStr"/>
       <c r="M147" s="12" t="inlineStr"/>
@@ -11780,7 +11780,7 @@
         <v>29</v>
       </c>
       <c r="K156" s="16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L156" s="16" t="inlineStr"/>
       <c r="M156" s="16" t="inlineStr"/>
@@ -12445,7 +12445,7 @@
         <v>20336.77</v>
       </c>
       <c r="P167" s="19" t="n">
-        <v>114.75</v>
+        <v>113.47</v>
       </c>
     </row>
   </sheetData>
@@ -13187,26 +13187,26 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>99</v>
+        <v>99.25</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>27.5</v>
+        <v>29.25</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>127.25</v>
+        <v>129.25</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
       <c r="G5" s="16" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>64.08</v>
+        <v>65.83</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-10.xlsx
+++ b/jira_export_2026-07-10.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>296 h</t>
+          <t>307 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1979,99 +1979,91 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J18" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M18" s="16" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L18" s="16" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr"/>
       <c r="N18" s="17" t="n">
-        <v>3207.7</v>
+        <v>0</v>
       </c>
       <c r="O18" s="17" t="n">
-        <v>4170.01</v>
+        <v>0</v>
       </c>
       <c r="P18" s="17" t="n">
-        <v>926.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en place de deux PAX</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ajout d'une régie et mise en place de deux PAX</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -2086,7 +2078,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
@@ -2098,52 +2090,52 @@
         <v>1</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34155</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>00171080</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N19" s="13" t="n">
-        <v>848.7</v>
-      </c>
-      <c r="O19" s="14" t="n">
-        <v>0</v>
+        <v>3207.7</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>4170.01</v>
       </c>
       <c r="P19" s="13" t="n">
-        <v>0</v>
+        <v>926.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en place de deux PAX</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Ajout d'une régie et mise en place de deux PAX</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -2158,12 +2150,12 @@
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J20" s="16" t="n">
@@ -2174,16 +2166,16 @@
       </c>
       <c r="L20" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34155</t>
         </is>
       </c>
       <c r="M20" s="16" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00171080</t>
         </is>
       </c>
       <c r="N20" s="17" t="n">
-        <v>353.5</v>
+        <v>848.7</v>
       </c>
       <c r="O20" s="14" t="n">
         <v>0</v>
@@ -2195,27 +2187,27 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP 2 + Pax</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -2235,7 +2227,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J21" s="12" t="n">
@@ -2246,16 +2238,16 @@
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N21" s="13" t="n">
-        <v>1242.5</v>
+        <v>353.5</v>
       </c>
       <c r="O21" s="14" t="n">
         <v>0</v>
@@ -2267,27 +2259,27 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
@@ -2302,64 +2294,64 @@
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J22" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="16" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L22" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M22" s="16" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N22" s="17" t="n">
-        <v>280</v>
+        <v>1242.5</v>
       </c>
       <c r="O22" s="14" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P22" s="17" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34045</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE NEUILLY SUR MARNE] - Migration GEODP PLACIER</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE NEUILLY SUR MARNE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP PLACIER</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -2374,7 +2366,7 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
@@ -2386,52 +2378,52 @@
         <v>1</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34054</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>00170461</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N23" s="13" t="n">
-        <v>850</v>
+        <v>280</v>
       </c>
       <c r="O23" s="14" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P23" s="13" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34045</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t>[COMMUNE DE NEUILLY SUR MARNE] - Migration GEODP PLACIER</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE NEUILLY SUR MARNE</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t>Migration GEODP PLACIER</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
@@ -2451,64 +2443,64 @@
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J24" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34054</t>
         </is>
       </c>
       <c r="M24" s="16" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170461</t>
         </is>
       </c>
       <c r="N24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="17" t="n">
-        <v>674</v>
+        <v>850</v>
+      </c>
+      <c r="O24" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="P24" s="17" t="n">
-        <v>674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -2518,64 +2510,64 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>4.25</v>
+        <v>1</v>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N25" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>497.16</v>
+        <v>674</v>
       </c>
       <c r="P25" s="13" t="n">
-        <v>116.98</v>
+        <v>674</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
@@ -2602,57 +2594,57 @@
         <v>1</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>0.5</v>
+        <v>7.25</v>
       </c>
       <c r="L26" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M26" s="16" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N26" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17" t="n">
-        <v>0</v>
+        <v>1242.9</v>
+      </c>
+      <c r="O26" s="14" t="n">
+        <v>497.16</v>
       </c>
       <c r="P26" s="17" t="n">
-        <v>0</v>
+        <v>68.56999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -2662,64 +2654,64 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>2.75</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N27" s="13" t="n">
-        <v>2100</v>
-      </c>
-      <c r="O27" s="14" t="n">
-        <v>1400</v>
+        <v>0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P27" s="13" t="n">
-        <v>509.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
@@ -2746,57 +2738,57 @@
         <v>1</v>
       </c>
       <c r="K28" s="16" t="n">
-        <v>1</v>
+        <v>2.75</v>
       </c>
       <c r="L28" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M28" s="16" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N28" s="17" t="n">
-        <v>340</v>
-      </c>
-      <c r="O28" s="17" t="n">
-        <v>340</v>
+        <v>2100</v>
+      </c>
+      <c r="O28" s="14" t="n">
+        <v>1400</v>
       </c>
       <c r="P28" s="17" t="n">
-        <v>340</v>
+        <v>509.09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -2806,49 +2798,49 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N29" s="13" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>219.1</v>
+        <v>340</v>
       </c>
       <c r="P29" s="13" t="n">
-        <v>109.55</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -2858,12 +2850,12 @@
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
@@ -2890,52 +2882,52 @@
         <v>1</v>
       </c>
       <c r="K30" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M30" s="16" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N30" s="17" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O30" s="14" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O30" s="17" t="n">
+        <v>219.1</v>
       </c>
       <c r="P30" s="17" t="n">
-        <v>0</v>
+        <v>109.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -2955,64 +2947,64 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="13" t="n">
-        <v>133.1</v>
+        <v>1890</v>
+      </c>
+      <c r="O31" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="P31" s="13" t="n">
-        <v>44.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33755</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
@@ -3022,69 +3014,69 @@
       </c>
       <c r="H32" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J32" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L32" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33764</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M32" s="16" t="inlineStr">
         <is>
-          <t>00169558</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N32" s="17" t="n">
-        <v>1365</v>
-      </c>
-      <c r="O32" s="14" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O32" s="17" t="n">
+        <v>133.1</v>
       </c>
       <c r="P32" s="17" t="n">
-        <v>0</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33755</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -3094,7 +3086,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
@@ -3106,20 +3098,20 @@
         <v>1</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33764</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169558</t>
         </is>
       </c>
       <c r="N33" s="13" t="n">
-        <v>920</v>
+        <v>1365</v>
       </c>
       <c r="O33" s="14" t="n">
         <v>0</v>
@@ -3131,27 +3123,27 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -3178,22 +3170,22 @@
         <v>1</v>
       </c>
       <c r="K34" s="16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L34" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M34" s="16" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N34" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="17" t="n">
+        <v>920</v>
+      </c>
+      <c r="O34" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="17" t="n">
@@ -3203,12 +3195,12 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -3218,12 +3210,12 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -3254,18 +3246,18 @@
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N35" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="13" t="n">
@@ -3275,32 +3267,32 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
+          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>Paiement CB + 3 PAX</t>
+          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
@@ -3315,27 +3307,27 @@
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J36" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L36" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33694</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="M36" s="16" t="inlineStr">
         <is>
-          <t>00169321</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="N36" s="17" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="O36" s="14" t="n">
         <v>0</v>
@@ -3347,27 +3339,27 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -3382,32 +3374,32 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33694</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169321</t>
         </is>
       </c>
       <c r="N37" s="13" t="n">
-        <v>4040</v>
+        <v>1500</v>
       </c>
       <c r="O37" s="14" t="n">
         <v>0</v>
@@ -3419,27 +3411,27 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -3454,7 +3446,7 @@
       </c>
       <c r="H38" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="16" t="inlineStr">
@@ -3466,20 +3458,20 @@
         <v>1</v>
       </c>
       <c r="K38" s="16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L38" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M38" s="16" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N38" s="17" t="n">
-        <v>407</v>
+        <v>4040</v>
       </c>
       <c r="O38" s="14" t="n">
         <v>0</v>
@@ -3491,32 +3483,32 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] Flux WFS</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Flux WFS (PS)</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -3531,27 +3523,27 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N39" s="13" t="n">
-        <v>895</v>
+        <v>407</v>
       </c>
       <c r="O39" s="14" t="n">
         <v>0</v>
@@ -3563,32 +3555,32 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
+          <t>[COMMUNE DE LILLE] Flux WFS</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>MM - Up - GeODP - PAX</t>
+          <t>MM - Up - LiExp - Flux WFS (PS)</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="16" t="inlineStr">
@@ -3614,16 +3606,16 @@
       </c>
       <c r="L40" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="M40" s="16" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="N40" s="17" t="n">
-        <v>500</v>
+        <v>895</v>
       </c>
       <c r="O40" s="14" t="n">
         <v>0</v>
@@ -3635,12 +3627,12 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -3650,12 +3642,12 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -3670,32 +3662,32 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J41" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="N41" s="13" t="n">
-        <v>1416</v>
+        <v>500</v>
       </c>
       <c r="O41" s="14" t="n">
         <v>0</v>
@@ -3707,32 +3699,32 @@
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="16" t="inlineStr">
@@ -3742,32 +3734,32 @@
       </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J42" s="16" t="n">
         <v>2</v>
       </c>
       <c r="K42" s="16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L42" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N42" s="17" t="n">
-        <v>171.4</v>
+        <v>1416</v>
       </c>
       <c r="O42" s="14" t="n">
         <v>0</v>
@@ -3779,32 +3771,32 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33461</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Buis-les-baronnies</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>INITIATION GEODP</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -3830,16 +3822,16 @@
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33465</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
-          <t>00167986</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N43" s="13" t="n">
-        <v>450</v>
+        <v>171.4</v>
       </c>
       <c r="O43" s="14" t="n">
         <v>0</v>
@@ -3851,32 +3843,32 @@
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33461</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>Mairie de Buis-les-baronnies</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t>INITIATION GEODP</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="16" t="inlineStr">
@@ -3898,22 +3890,22 @@
         <v>2</v>
       </c>
       <c r="K44" s="16" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L44" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33465</t>
         </is>
       </c>
       <c r="M44" s="16" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00167986</t>
         </is>
       </c>
       <c r="N44" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="O44" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="17" t="n">
@@ -3923,32 +3915,32 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -3958,64 +3950,64 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J45" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N45" s="13" t="n">
-        <v>417.4</v>
+        <v>0</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>1252.2</v>
+        <v>0</v>
       </c>
       <c r="P45" s="13" t="n">
-        <v>834.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33408</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>[Commune de Flayosc] - Migration 3 activités GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Commune de Flayosc</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>Migration 3 activités GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
@@ -4042,57 +4034,57 @@
         <v>2</v>
       </c>
       <c r="K46" s="16" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="L46" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33415</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M46" s="16" t="inlineStr">
         <is>
-          <t>00167809</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N46" s="17" t="n">
-        <v>0</v>
+        <v>417.4</v>
       </c>
       <c r="O46" s="17" t="n">
-        <v>0</v>
+        <v>1252.2</v>
       </c>
       <c r="P46" s="17" t="n">
-        <v>0</v>
+        <v>834.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33408</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[Commune de Flayosc] - Migration 3 activités GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>Commune de Flayosc</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>Migration 3 activités GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -4102,12 +4094,12 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J47" s="12" t="n">
@@ -4118,33 +4110,33 @@
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33415</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167809</t>
         </is>
       </c>
       <c r="N47" s="13" t="n">
-        <v>617.04</v>
+        <v>0</v>
       </c>
       <c r="O47" s="13" t="n">
-        <v>1028.4</v>
+        <v>0</v>
       </c>
       <c r="P47" s="13" t="n">
-        <v>411.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33363</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
@@ -4154,12 +4146,12 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Vérif</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
@@ -4169,7 +4161,7 @@
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H48" s="16" t="inlineStr">
@@ -4179,36 +4171,44 @@
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J48" s="16" t="n">
         <v>2</v>
       </c>
       <c r="K48" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L48" s="16" t="inlineStr"/>
-      <c r="M48" s="16" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L48" s="16" t="inlineStr">
+        <is>
+          <t>PDMDEP-33390</t>
+        </is>
+      </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>00167823</t>
+        </is>
+      </c>
       <c r="N48" s="17" t="n">
-        <v>0</v>
+        <v>617.04</v>
       </c>
       <c r="O48" s="17" t="n">
-        <v>0</v>
+        <v>1028.4</v>
       </c>
       <c r="P48" s="17" t="n">
-        <v>0</v>
+        <v>411.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33348</t>
+          <t>PDMDEP-33363</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
+          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modélisation + Modif Marianne </t>
+          <t>MM - Up - LiExp - Vérif</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -4243,29 +4243,21 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="J49" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33352</t>
-        </is>
-      </c>
-      <c r="M49" s="12" t="inlineStr">
-        <is>
-          <t>00167402</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L49" s="12" t="inlineStr"/>
+      <c r="M49" s="12" t="inlineStr"/>
       <c r="N49" s="13" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P49" s="13" t="n">
@@ -4275,32 +4267,32 @@
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33348</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
@@ -4310,12 +4302,12 @@
       </c>
       <c r="H50" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="J50" s="16" t="n">
@@ -4326,16 +4318,16 @@
       </c>
       <c r="L50" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33352</t>
         </is>
       </c>
       <c r="M50" s="16" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167402</t>
         </is>
       </c>
       <c r="N50" s="17" t="n">
-        <v>149</v>
+        <v>171.4</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>0</v>
@@ -4347,32 +4339,32 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -4382,32 +4374,32 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J51" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N51" s="13" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O51" s="14" t="n">
         <v>0</v>
@@ -4470,16 +4462,16 @@
       </c>
       <c r="L52" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M52" s="16" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N52" s="17" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="O52" s="14" t="n">
         <v>0</v>
@@ -4491,27 +4483,27 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33203</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] - LiExp - Crédits d'heure + TDC MV</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>LiExp - Crédits d'heure + TDC MV</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -4531,7 +4523,7 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J53" s="12" t="n">
@@ -4542,18 +4534,18 @@
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33207</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
-          <t>00166553</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N53" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="13" t="n">
+        <v>600</v>
+      </c>
+      <c r="O53" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="13" t="n">
@@ -4563,32 +4555,32 @@
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33203</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[CD 38] - LiExp - Crédits d'heure + TDC MV</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>LiExp - Crédits d'heure + TDC MV</t>
         </is>
       </c>
       <c r="F54" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
@@ -4598,64 +4590,64 @@
       </c>
       <c r="H54" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="J54" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" s="16" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L54" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33207</t>
         </is>
       </c>
       <c r="M54" s="16" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166553</t>
         </is>
       </c>
       <c r="N54" s="17" t="n">
-        <v>3621</v>
+        <v>0</v>
       </c>
       <c r="O54" s="17" t="n">
-        <v>4224.5</v>
+        <v>0</v>
       </c>
       <c r="P54" s="17" t="n">
-        <v>1207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -4675,7 +4667,7 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J55" s="12" t="n">
@@ -4686,53 +4678,53 @@
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M55" s="12" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N55" s="13" t="n">
-        <v>1618.5</v>
+        <v>3621</v>
       </c>
       <c r="O55" s="13" t="n">
-        <v>1618.5</v>
+        <v>4224.5</v>
       </c>
       <c r="P55" s="13" t="n">
-        <v>462.43</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
@@ -4742,69 +4734,69 @@
       </c>
       <c r="H56" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J56" s="16" t="n">
         <v>3</v>
       </c>
       <c r="K56" s="16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L56" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M56" s="16" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N56" s="17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O56" s="14" t="n">
-        <v>0</v>
+        <v>1618.5</v>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>1618.5</v>
       </c>
       <c r="P56" s="17" t="n">
-        <v>0</v>
+        <v>462.43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -4814,7 +4806,7 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="12" t="inlineStr">
@@ -4826,22 +4818,22 @@
         <v>3</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N57" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O57" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="13" t="n">
@@ -4851,27 +4843,27 @@
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32902</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMANDE PAX </t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
@@ -4886,12 +4878,12 @@
       </c>
       <c r="H58" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J58" s="16" t="n">
@@ -4902,12 +4894,12 @@
       </c>
       <c r="L58" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32910</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M58" s="16" t="inlineStr">
         <is>
-          <t>00159637</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N58" s="17" t="n">
@@ -4923,12 +4915,12 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32902</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -4938,12 +4930,12 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t xml:space="preserve">COMMANDE PAX </t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -4963,29 +4955,29 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="J59" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32910</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00159637</t>
         </is>
       </c>
       <c r="N59" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="O59" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="13" t="n">
@@ -4995,12 +4987,12 @@
     <row r="60">
       <c r="A60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
@@ -5010,12 +5002,12 @@
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F60" s="16" t="inlineStr">
@@ -5035,7 +5027,7 @@
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J60" s="16" t="n">
@@ -5046,16 +5038,16 @@
       </c>
       <c r="L60" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M60" s="16" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N60" s="17" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="O60" s="14" t="n">
         <v>0</v>
@@ -5067,32 +5059,32 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -5107,27 +5099,27 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J61" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="O61" s="14" t="n">
         <v>0</v>
@@ -5139,12 +5131,12 @@
     <row r="62">
       <c r="A62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
@@ -5154,7 +5146,7 @@
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr">
@@ -5186,20 +5178,20 @@
         <v>3</v>
       </c>
       <c r="K62" s="16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L62" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M62" s="16" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N62" s="17" t="n">
-        <v>564</v>
+        <v>705</v>
       </c>
       <c r="O62" s="14" t="n">
         <v>0</v>
@@ -5211,32 +5203,32 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -5246,7 +5238,7 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
@@ -5258,37 +5250,37 @@
         <v>3</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
-        <v>2138.2</v>
+        <v>564</v>
       </c>
       <c r="O63" s="14" t="n">
-        <v>1375.2</v>
+        <v>0</v>
       </c>
       <c r="P63" s="13" t="n">
-        <v>305.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
@@ -5298,12 +5290,12 @@
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
@@ -5318,69 +5310,69 @@
       </c>
       <c r="H64" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J64" s="16" t="n">
         <v>3</v>
       </c>
       <c r="K64" s="16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L64" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M64" s="16" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N64" s="17" t="n">
-        <v>283.5</v>
+        <v>2138.2</v>
       </c>
       <c r="O64" s="14" t="n">
-        <v>0</v>
+        <v>1375.2</v>
       </c>
       <c r="P64" s="17" t="n">
-        <v>0</v>
+        <v>305.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -5390,32 +5382,32 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J65" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
-        <v>548.4</v>
+        <v>283.5</v>
       </c>
       <c r="O65" s="14" t="n">
         <v>0</v>
@@ -5427,32 +5419,32 @@
     <row r="66">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F66" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr">
@@ -5462,7 +5454,7 @@
       </c>
       <c r="H66" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="16" t="inlineStr">
@@ -5474,20 +5466,20 @@
         <v>3</v>
       </c>
       <c r="K66" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M66" s="16" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N66" s="17" t="n">
-        <v>552</v>
+        <v>548.4</v>
       </c>
       <c r="O66" s="14" t="n">
         <v>0</v>
@@ -5499,32 +5491,32 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -5534,32 +5526,32 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J67" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N67" s="13" t="n">
-        <v>142.1</v>
+        <v>552</v>
       </c>
       <c r="O67" s="14" t="n">
         <v>0</v>
@@ -5571,32 +5563,32 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F68" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="16" t="inlineStr">
@@ -5606,32 +5598,32 @@
       </c>
       <c r="H68" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J68" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K68" s="16" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L68" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M68" s="16" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N68" s="17" t="n">
-        <v>1868</v>
+        <v>142.1</v>
       </c>
       <c r="O68" s="14" t="n">
         <v>0</v>
@@ -5643,32 +5635,32 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -5678,32 +5670,32 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J69" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
-        <v>882.5</v>
+        <v>1868</v>
       </c>
       <c r="O69" s="14" t="n">
         <v>0</v>
@@ -5715,27 +5707,27 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F70" s="16" t="inlineStr">
@@ -5755,29 +5747,29 @@
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J70" s="16" t="n">
         <v>4</v>
       </c>
       <c r="K70" s="16" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="L70" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M70" s="16" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N70" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="17" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="O70" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="17" t="n">
@@ -5787,32 +5779,32 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -5822,35 +5814,35 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J71" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N71" s="13" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="P71" s="13" t="n">
         <v>0</v>
@@ -5859,32 +5851,32 @@
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F72" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="16" t="inlineStr">
@@ -5894,69 +5886,69 @@
       </c>
       <c r="H72" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J72" s="16" t="n">
         <v>4</v>
       </c>
       <c r="K72" s="16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="L72" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M72" s="16" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N72" s="17" t="n">
-        <v>1046.5</v>
-      </c>
-      <c r="O72" s="14" t="n">
-        <v>637</v>
+        <v>450</v>
+      </c>
+      <c r="O72" s="17" t="n">
+        <v>450</v>
       </c>
       <c r="P72" s="17" t="n">
-        <v>74.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -5966,64 +5958,64 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>3.25</v>
+        <v>8.5</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>765</v>
+        <v>1046.5</v>
       </c>
       <c r="O73" s="14" t="n">
-        <v>0</v>
+        <v>637</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>0</v>
+        <v>74.94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F74" s="16" t="inlineStr">
@@ -6050,52 +6042,52 @@
         <v>4</v>
       </c>
       <c r="K74" s="16" t="n">
-        <v>0.75</v>
+        <v>3.25</v>
       </c>
       <c r="L74" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M74" s="16" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N74" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="17" t="n">
-        <v>100</v>
+        <v>765</v>
+      </c>
+      <c r="O74" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="P74" s="17" t="n">
-        <v>133.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -6110,12 +6102,12 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
@@ -6126,33 +6118,33 @@
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>407</v>
-      </c>
-      <c r="O75" s="14" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O75" s="13" t="n">
+        <v>100</v>
       </c>
       <c r="P75" s="13" t="n">
-        <v>0</v>
+        <v>133.33</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
@@ -6162,12 +6154,12 @@
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F76" s="16" t="inlineStr">
@@ -6182,32 +6174,32 @@
       </c>
       <c r="H76" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J76" s="16" t="n">
         <v>4</v>
       </c>
       <c r="K76" s="16" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L76" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M76" s="16" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N76" s="17" t="n">
-        <v>257.15</v>
+        <v>407</v>
       </c>
       <c r="O76" s="14" t="n">
         <v>0</v>
@@ -6219,32 +6211,32 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -6254,32 +6246,32 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>440.38</v>
+        <v>257.15</v>
       </c>
       <c r="O77" s="14" t="n">
         <v>0</v>
@@ -6291,32 +6283,32 @@
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E78" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F78" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr">
@@ -6326,12 +6318,12 @@
       </c>
       <c r="H78" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="16" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J78" s="16" t="n">
@@ -6342,16 +6334,16 @@
       </c>
       <c r="L78" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M78" s="16" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N78" s="17" t="n">
-        <v>285</v>
+        <v>440.38</v>
       </c>
       <c r="O78" s="14" t="n">
         <v>0</v>
@@ -6363,32 +6355,32 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6403,7 +6395,7 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
@@ -6414,16 +6406,16 @@
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O79" s="14" t="n">
         <v>0</v>
@@ -8702,7 +8694,7 @@
         <v>8</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
@@ -8774,7 +8766,7 @@
         <v>8</v>
       </c>
       <c r="K112" s="16" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="L112" s="16" t="inlineStr">
         <is>
@@ -8846,7 +8838,7 @@
         <v>8</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
@@ -8918,7 +8910,7 @@
         <v>8</v>
       </c>
       <c r="K114" s="16" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="L114" s="16" t="inlineStr">
         <is>
@@ -8990,7 +8982,7 @@
         <v>8</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
@@ -11136,7 +11128,7 @@
         <v>19</v>
       </c>
       <c r="K146" s="16" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L146" s="16" t="inlineStr"/>
       <c r="M146" s="16" t="inlineStr"/>
@@ -11718,7 +11710,7 @@
         <v>29</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L155" s="12" t="inlineStr"/>
       <c r="M155" s="12" t="inlineStr"/>
@@ -12032,7 +12024,7 @@
         <v>34</v>
       </c>
       <c r="K160" s="16" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="L160" s="16" t="inlineStr">
         <is>
@@ -12439,13 +12431,13 @@
       <c r="L167" s="18" t="inlineStr"/>
       <c r="M167" s="18" t="inlineStr"/>
       <c r="N167" s="19" t="n">
-        <v>70958.95999999999</v>
+        <v>70876.85999999999</v>
       </c>
       <c r="O167" s="19" t="n">
         <v>20336.77</v>
       </c>
       <c r="P167" s="19" t="n">
-        <v>113.47</v>
+        <v>109.35</v>
       </c>
     </row>
   </sheetData>
@@ -13187,16 +13179,16 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>99.25</v>
+        <v>104</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>29.25</v>
+        <v>30.75</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>129.25</v>
+        <v>136</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>34.5</v>
@@ -13206,7 +13198,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13240,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>65.83</v>
+        <v>70.33</v>
       </c>
     </row>
   </sheetData>
